--- a/astro-site/public/dl/catering-checklist-templates/BONUS-01-catering-pre-event-briefing-template.xlsx
+++ b/astro-site/public/dl/catering-checklist-templates/BONUS-01-catering-pre-event-briefing-template.xlsx
@@ -880,7 +880,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Review the full menu with the team: starters, mains, desserts</t>
+          <t>Review the full menu with the team: appetizers, entrées, desserts</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
@@ -1294,7 +1294,7 @@
   </mergeCells>
   <conditionalFormatting sqref="A6:G34">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$E6="✓"</formula>
+      <formula>AND($E6="✓",$B6&lt;&gt;"Task")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
